--- a/SMH_ED_OHIP_Billing_Apr2026.xlsx
+++ b/SMH_ED_OHIP_Billing_Apr2026.xlsx
@@ -11,7 +11,7 @@
     <sheet name="By Category" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Codes'!$A$1:$E$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Codes'!$A$1:$E$234</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By Category'!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Foreign body removal – eye</t>
+          <t>Foreign body removal – eye (1 FB)</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
@@ -4057,37 +4057,41 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Z432A</t>
+          <t>Z848</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Foreign body removal – vagina (GA)</t>
+          <t>Foreign body removal – eye (2 FBs)</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Foreign Bodies</t>
         </is>
       </c>
-      <c r="E152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Exact fee $45.00 (MOH Jan 2025)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>S547</t>
+          <t>Z432A</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Foreign body removal – urethra</t>
+          <t>Foreign body removal – vagina (GA)</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
@@ -4099,64 +4103,64 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>E023C</t>
+          <t>S547</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Foreign body removal – vagina with sedation</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Foreign body removal – urethra</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>171</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
           <t>Foreign Bodies</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>6 anaesthesia units</t>
-        </is>
-      </c>
+      <c r="E154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>G420</t>
+          <t>E023C</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Ear syringe/irrigation</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="n">
-        <v>11</v>
+          <t>Foreign body removal – vagina with sedation</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr"/>
+          <t>Foreign Bodies</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>6 anaesthesia units</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>G403</t>
+          <t>G420</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Epley manoeuvre</t>
+          <t>Ear syringe/irrigation</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -4168,16 +4172,16 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Z315</t>
+          <t>G403</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Anterior nasal pack</t>
+          <t>Epley manoeuvre</t>
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
@@ -4189,16 +4193,16 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Z321</t>
+          <t>Z315</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Direct laryngoscopy</t>
+          <t>Anterior nasal pack</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
@@ -4210,16 +4214,16 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Z316</t>
+          <t>Z321</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Posterior nasal pack</t>
+          <t>Direct laryngoscopy</t>
         </is>
       </c>
       <c r="C159" s="7" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
@@ -4231,16 +4235,16 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Z322</t>
+          <t>Z316</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Direct laryngoscopy with FB removal</t>
+          <t>Posterior nasal pack</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -4252,16 +4256,16 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Z314</t>
+          <t>Z322</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Nasal cautery</t>
+          <t>Direct laryngoscopy with FB removal</t>
         </is>
       </c>
       <c r="C161" s="7" t="n">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
@@ -4273,16 +4277,16 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Z324</t>
+          <t>Z314</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Indirect laryngoscopy with FB removal</t>
+          <t>Nasal cautery</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -4294,16 +4298,16 @@
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>F136</t>
+          <t>Z324</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Nasal fracture reduction</t>
+          <t>Indirect laryngoscopy with FB removal</t>
         </is>
       </c>
       <c r="C163" s="7" t="n">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
@@ -4315,16 +4319,16 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>D062</t>
+          <t>F136</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>TMJ reduction</t>
+          <t>Nasal fracture reduction</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -4336,41 +4340,37 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>D062</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>Phalanx finger fracture – closed, no reduction</t>
+          <t>TMJ reduction</t>
         </is>
       </c>
       <c r="C165" s="7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>Fractures – Upper Extremity</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
-        </is>
-      </c>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F004</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Phalanx finger fracture – closed, with reduction</t>
+          <t>Phalanx finger fracture – closed, no reduction</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -4379,23 +4379,23 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Ortho f/u = 75%; Exact fee $99.25 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>E558</t>
+          <t>F005</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>Phalanx finger – each addl fracture with reduction</t>
+          <t>Phalanx finger fracture – closed, with reduction</t>
         </is>
       </c>
       <c r="C167" s="7" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
@@ -4404,23 +4404,23 @@
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $22.25 (MOH Jan 2025)</t>
+          <t>Ortho f/u = 75%; Exact fee $99.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>E558</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Phalanx finger fracture – open, with reduction</t>
+          <t>Phalanx finger – each addl fracture with reduction</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>298</v>
+        <v>22</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -4429,23 +4429,23 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $298.45 (MOH Jan 2025)</t>
+          <t>Exact fee $22.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>F007</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>Metacarpal fracture – no reduction</t>
+          <t>Phalanx finger fracture – open, with reduction</t>
         </is>
       </c>
       <c r="C169" s="7" t="n">
-        <v>49</v>
+        <v>298</v>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
@@ -4454,23 +4454,23 @@
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
+          <t>Exact fee $298.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F008</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Metacarpal fracture – with reduction</t>
+          <t>Metacarpal fracture – no reduction</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -4479,23 +4479,23 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $99.25 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F009</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>Bennett's fracture – no reduction</t>
+          <t>Metacarpal fracture – with reduction</t>
         </is>
       </c>
       <c r="C171" s="7" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
@@ -4504,23 +4504,23 @@
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
+          <t>Exact fee $99.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F012</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Bennett's fracture – with reduction</t>
+          <t>Bennett's fracture – no reduction</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -4529,23 +4529,23 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $119.80 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>Scaphoid fracture – no reduction</t>
+          <t>Bennett's fracture – with reduction</t>
         </is>
       </c>
       <c r="C173" s="7" t="n">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
@@ -4554,19 +4554,19 @@
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
+          <t>Exact fee $119.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>F102</t>
+          <t>F018</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Other carpal fracture – no reduction</t>
+          <t>Scaphoid fracture – no reduction</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
@@ -4586,16 +4586,16 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F102</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>Other carpal fracture – with reduction</t>
+          <t>Other carpal fracture – no reduction</t>
         </is>
       </c>
       <c r="C175" s="7" t="n">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
@@ -4604,23 +4604,23 @@
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $115.10 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>F027</t>
+          <t>F016</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Colles/Smith fracture – no reduction</t>
+          <t>Other carpal fracture – with reduction</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -4629,23 +4629,23 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $67.75 (MOH Jan 2025)</t>
+          <t>Exact fee $115.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>F027</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>Colles/Smith fracture – with reduction</t>
+          <t>Colles/Smith fracture – no reduction</t>
         </is>
       </c>
       <c r="C177" s="7" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
@@ -4654,23 +4654,23 @@
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $109.45 (MOH Jan 2025)</t>
+          <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>F046</t>
+          <t>F028</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Colles/Smith fracture – with reduction + sedation</t>
+          <t>Colles/Smith fracture – with reduction</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -4679,23 +4679,23 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $149.35 (MOH Jan 2025)</t>
+          <t>Exact fee $109.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>F031</t>
+          <t>F046</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>Radius or ulna fracture – no reduction</t>
+          <t>Colles/Smith fracture – with reduction + sedation</t>
         </is>
       </c>
       <c r="C179" s="7" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
@@ -4704,23 +4704,23 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $81.30 (MOH Jan 2025)</t>
+          <t>Exact fee $149.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F031</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Radius or ulna fracture – with reduction</t>
+          <t>Radius or ulna fracture – no reduction</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
@@ -4729,23 +4729,23 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $117.85 (MOH Jan 2025)</t>
+          <t>Exact fee $81.30 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>F034</t>
+          <t>F032</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>Olecranon fracture – no reduction</t>
+          <t>Radius or ulna fracture – with reduction</t>
         </is>
       </c>
       <c r="C181" s="7" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
@@ -4754,23 +4754,23 @@
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $126.25 (MOH Jan 2025)</t>
+          <t>Exact fee $117.85 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>F035</t>
+          <t>F034</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Olecranon fracture – with reduction</t>
+          <t>Olecranon fracture – no reduction</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -4779,23 +4779,23 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $129.00 (MOH Jan 2025)</t>
+          <t>Exact fee $126.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>F029</t>
+          <t>F035</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Epicondyle fracture (no cast) – no reduction</t>
+          <t>Olecranon fracture – with reduction</t>
         </is>
       </c>
       <c r="C183" s="7" t="n">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
@@ -4804,23 +4804,23 @@
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $67.75 (MOH Jan 2025)</t>
+          <t>Exact fee $129.00 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F029</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Epicondyle fracture (no cast) – with reduction</t>
+          <t>Epicondyle fracture (no cast) – no reduction</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -4829,23 +4829,23 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $126.25 (MOH Jan 2025)</t>
+          <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>F042</t>
+          <t>F037</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>Humeral shaft fracture (no cast) – no reduction</t>
+          <t>Epicondyle fracture (no cast) – with reduction</t>
         </is>
       </c>
       <c r="C185" s="7" t="n">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
@@ -4854,23 +4854,23 @@
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $67.80 (MOH Jan 2025)</t>
+          <t>Exact fee $126.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>F043</t>
+          <t>F042</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Humeral shaft fracture (no cast) – with reduction</t>
+          <t>Humeral shaft fracture (no cast) – no reduction</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
@@ -4879,23 +4879,23 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $147.60 (MOH Jan 2025)</t>
+          <t>Exact fee $67.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>F053</t>
+          <t>F043</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Humeral neck fracture (no cast) – no reduction</t>
+          <t>Humeral shaft fracture (no cast) – with reduction</t>
         </is>
       </c>
       <c r="C187" s="7" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
@@ -4904,23 +4904,23 @@
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $67.80 (MOH Jan 2025)</t>
+          <t>Exact fee $147.60 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>F054</t>
+          <t>F053</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Humeral neck fracture (no cast) – with reduction</t>
+          <t>Humeral neck fracture (no cast) – no reduction</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -4929,48 +4929,48 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $133.60 (MOH Jan 2025)</t>
+          <t>Exact fee $67.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>F134</t>
+          <t>F054</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>Pelvis fracture with pelvic binder – with reduction</t>
+          <t>Humeral neck fracture (no cast) – with reduction</t>
         </is>
       </c>
       <c r="C189" s="7" t="n">
-        <v>442</v>
+        <v>134</v>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Fractures – Lower Extremity</t>
+          <t>Fractures – Upper Extremity</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>No fee for no-reduction code; Exact fee $442.45 (MOH Jan 2025)</t>
+          <t>Exact fee $133.60 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F134</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Femur fracture – with reduction</t>
+          <t>Pelvis fracture with pelvic binder – with reduction</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
@@ -4979,23 +4979,23 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>No fee for no-reduction code; Exact fee $407.35 (MOH Jan 2025)</t>
+          <t>No fee for no-reduction code; Exact fee $442.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>F085</t>
+          <t>F095</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>Patella fracture (no cast) – no reduction</t>
+          <t>Femur fracture – with reduction</t>
         </is>
       </c>
       <c r="C191" s="7" t="n">
-        <v>68</v>
+        <v>407</v>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
@@ -5004,23 +5004,23 @@
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $67.75 (MOH Jan 2025)</t>
+          <t>No fee for no-reduction code; Exact fee $407.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>F078</t>
+          <t>F085</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Tibia ± fibula fracture – no reduction</t>
+          <t>Patella fracture (no cast) – no reduction</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
@@ -5029,23 +5029,23 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $115.95 (MOH Jan 2025)</t>
+          <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>F079</t>
+          <t>F078</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>Tibia ± fibula fracture – with reduction</t>
+          <t>Tibia ± fibula fracture – no reduction</t>
         </is>
       </c>
       <c r="C193" s="7" t="n">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
@@ -5054,23 +5054,23 @@
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $180.05 (MOH Jan 2025)</t>
+          <t>Exact fee $115.95 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>F082</t>
+          <t>F079</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Fibula fracture – no reduction</t>
+          <t>Tibia ± fibula fracture – with reduction</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
@@ -5079,23 +5079,23 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $67.75 (MOH Jan 2025)</t>
+          <t>Exact fee $180.05 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>F083</t>
+          <t>F082</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>Fibula fracture – with reduction</t>
+          <t>Fibula fracture – no reduction</t>
         </is>
       </c>
       <c r="C195" s="7" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
@@ -5104,23 +5104,23 @@
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $101.25 (MOH Jan 2025)</t>
+          <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>F074</t>
+          <t>F083</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Ankle fracture – no reduction</t>
+          <t>Fibula fracture – with reduction</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -5129,23 +5129,23 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $67.75 (MOH Jan 2025)</t>
+          <t>Exact fee $101.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>F075</t>
+          <t>F074</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Ankle fracture – with reduction</t>
+          <t>Ankle fracture – no reduction</t>
         </is>
       </c>
       <c r="C197" s="7" t="n">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
@@ -5154,23 +5154,23 @@
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $144.80 (MOH Jan 2025)</t>
+          <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>F104</t>
+          <t>F075</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Ankle fracture with plafond burst – with reduction</t>
+          <t>Ankle fracture – with reduction</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>242</v>
+        <v>145</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -5179,23 +5179,23 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $242.25 (MOH Jan 2025)</t>
+          <t>Exact fee $144.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>F070</t>
+          <t>F104</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>Calcaneus fracture – no reduction</t>
+          <t>Ankle fracture with plafond burst – with reduction</t>
         </is>
       </c>
       <c r="C199" s="7" t="n">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
@@ -5204,23 +5204,23 @@
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $97.35 (MOH Jan 2025)</t>
+          <t>Exact fee $242.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>F071</t>
+          <t>F070</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Calcaneus fracture – with reduction</t>
+          <t>Calcaneus fracture – no reduction</t>
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
@@ -5229,23 +5229,23 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $161.45 (MOH Jan 2025)</t>
+          <t>Exact fee $97.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>F061</t>
+          <t>F071</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>Metatarsal fracture (no cast) – no reduction</t>
+          <t>Calcaneus fracture – with reduction</t>
         </is>
       </c>
       <c r="C201" s="7" t="n">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
@@ -5254,23 +5254,23 @@
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
+          <t>Exact fee $161.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>F062</t>
+          <t>F061</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Metatarsal fracture (with cast) – no reduction</t>
+          <t>Metatarsal fracture (no cast) – no reduction</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
@@ -5279,23 +5279,23 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $67.75 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>F063</t>
+          <t>F062</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Metatarsal fracture (with cast) – with reduction</t>
+          <t>Metatarsal fracture (with cast) – no reduction</t>
         </is>
       </c>
       <c r="C203" s="7" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
@@ -5304,19 +5304,19 @@
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $98.35 (MOH Jan 2025)</t>
+          <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>F066</t>
+          <t>F063</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Tarsal bone fracture – no reduction</t>
+          <t>Metatarsal fracture (with cast) – with reduction</t>
         </is>
       </c>
       <c r="C204" s="4" t="n">
@@ -5329,23 +5329,23 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $98.10 (MOH Jan 2025)</t>
+          <t>Exact fee $98.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>F067</t>
+          <t>F066</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>Tarsal bone fracture – with reduction</t>
+          <t>Tarsal bone fracture – no reduction</t>
         </is>
       </c>
       <c r="C205" s="7" t="n">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
@@ -5354,23 +5354,23 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $165.20 (MOH Jan 2025)</t>
+          <t>Exact fee $98.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>F056</t>
+          <t>F067</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Phalanx toe fracture – no reduction</t>
+          <t>Tarsal bone fracture – with reduction</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
@@ -5379,23 +5379,23 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
+          <t>Exact fee $165.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>F058</t>
+          <t>F056</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>Phalanx toe fracture – with reduction</t>
+          <t>Phalanx toe fracture – no reduction</t>
         </is>
       </c>
       <c r="C207" s="7" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
@@ -5404,23 +5404,23 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $72.35 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>E560</t>
+          <t>F058</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Phalanx toe – each addl, no reduction</t>
+          <t>Phalanx toe fracture – with reduction</t>
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
@@ -5429,23 +5429,23 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $12.05 (MOH Jan 2025)</t>
+          <t>Exact fee $72.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>E561</t>
+          <t>E560</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>Phalanx toe – each addl, with reduction</t>
+          <t>Phalanx toe – each addl, no reduction</t>
         </is>
       </c>
       <c r="C209" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
@@ -5454,48 +5454,48 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $14.90 (MOH Jan 2025)</t>
+          <t>Exact fee $12.05 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>D001</t>
+          <t>E561</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Phalanx finger dislocation reduction</t>
+          <t>Phalanx toe – each addl, with reduction</t>
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Dislocation Reductions</t>
+          <t>Fractures – Lower Extremity</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $57.50 (MOH Jan 2025)</t>
+          <t>Exact fee $14.90 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>E576</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>Phalanx finger – each addl dislocation</t>
+          <t>Phalanx finger dislocation reduction</t>
         </is>
       </c>
       <c r="C211" s="7" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
@@ -5504,23 +5504,23 @@
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $10.25 (MOH Jan 2025)</t>
+          <t>Exact fee $57.50 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>E576</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Phalanx finger dislocation reduction – open</t>
+          <t>Phalanx finger – each addl dislocation</t>
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
@@ -5529,23 +5529,23 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $196.50 (MOH Jan 2025)</t>
+          <t>Exact fee $10.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>Metacarpophalangeal dislocation reduction</t>
+          <t>Phalanx finger dislocation reduction – open</t>
         </is>
       </c>
       <c r="C213" s="7" t="n">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
@@ -5554,23 +5554,23 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $57.50 (MOH Jan 2025)</t>
+          <t>Exact fee $196.50 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Carpal dislocation reduction</t>
+          <t>Metacarpophalangeal dislocation reduction</t>
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
@@ -5579,23 +5579,23 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $128.05 (MOH Jan 2025)</t>
+          <t>Exact fee $57.50 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>D012</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Pulled elbow reduction</t>
+          <t>Carpal dislocation reduction</t>
         </is>
       </c>
       <c r="C215" s="7" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
@@ -5604,23 +5604,23 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $39.00 (MOH Jan 2025)</t>
+          <t>Exact fee $128.05 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D012</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Elbow dislocation reduction</t>
+          <t>Pulled elbow reduction</t>
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
@@ -5629,23 +5629,23 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $84.45 (MOH Jan 2025)</t>
+          <t>Exact fee $39.00 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>D015</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>Shoulder dislocation reduction – no sedation</t>
+          <t>Elbow dislocation reduction</t>
         </is>
       </c>
       <c r="C217" s="7" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
@@ -5654,23 +5654,23 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $49.20 (MOH Jan 2025)</t>
+          <t>Exact fee $84.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>D016</t>
+          <t>D015</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Shoulder dislocation reduction – with sedation</t>
+          <t>Shoulder dislocation reduction – no sedation</t>
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
@@ -5679,23 +5679,23 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $111.40 (MOH Jan 2025)</t>
+          <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>D014</t>
+          <t>D016</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>A/C or S/C joint – no reduction</t>
+          <t>Shoulder dislocation reduction – with sedation</t>
         </is>
       </c>
       <c r="C219" s="7" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
@@ -5704,23 +5704,23 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $67.80 (MOH Jan 2025)</t>
+          <t>Exact fee $111.40 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D014</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Hip dislocation reduction</t>
+          <t>A/C or S/C joint – no reduction</t>
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
@@ -5729,23 +5729,23 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $268.25 (MOH Jan 2025)</t>
+          <t>Exact fee $67.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>Knee dislocation reduction (no cast)</t>
+          <t>Hip dislocation reduction</t>
         </is>
       </c>
       <c r="C221" s="7" t="n">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
@@ -5754,23 +5754,23 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $207.90 (MOH Jan 2025)</t>
+          <t>Exact fee $268.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Patella dislocation – no sedation, no cast</t>
+          <t>Knee dislocation reduction (no cast)</t>
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>62</v>
+        <v>208</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -5779,23 +5779,23 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $62.20 (MOH Jan 2025)</t>
+          <t>Exact fee $207.90 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D040</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Patella dislocation – with sedation, no cast</t>
+          <t>Patella dislocation – no sedation, no cast</t>
         </is>
       </c>
       <c r="C223" s="7" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
@@ -5804,23 +5804,23 @@
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $97.35 (MOH Jan 2025)</t>
+          <t>Exact fee $62.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Ankle dislocation reduction</t>
+          <t>Patella dislocation – with sedation, no cast</t>
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
@@ -5829,23 +5829,23 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $111.35 (MOH Jan 2025)</t>
+          <t>Exact fee $97.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>D026</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>Tarso-metatarsal dislocation reduction (no cast)</t>
+          <t>Ankle dislocation reduction</t>
         </is>
       </c>
       <c r="C225" s="7" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
@@ -5854,23 +5854,23 @@
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Exact fee $147.60 (MOH Jan 2025)</t>
+          <t>Exact fee $111.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>D030</t>
+          <t>D026</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Metatarsophalangeal dislocation reduction</t>
+          <t>Tarso-metatarsal dislocation reduction (no cast)</t>
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
@@ -5879,19 +5879,19 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Exact fee $57.50 (MOH Jan 2025)</t>
+          <t>Exact fee $147.60 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>D027</t>
+          <t>D030</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>Interphalangeal toe dislocation reduction</t>
+          <t>Metatarsophalangeal dislocation reduction</t>
         </is>
       </c>
       <c r="C227" s="7" t="n">
@@ -5911,41 +5911,41 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Z201</t>
+          <t>D027</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Finger splint/cast</t>
+          <t>Interphalangeal toe dislocation reduction</t>
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Splints &amp; Casts</t>
+          <t>Dislocation Reductions</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Only if no F or D code billed; Exact fee $10.25 (MOH Jan 2025)</t>
+          <t>Exact fee $57.50 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>Z202</t>
+          <t>Z201</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>Hand splint/cast</t>
+          <t>Finger splint/cast</t>
         </is>
       </c>
       <c r="C229" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
@@ -5954,23 +5954,23 @@
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>Only if no F or D code billed; Exact fee $14.90 (MOH Jan 2025)</t>
+          <t>Only if no F or D code billed; Exact fee $10.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Z203</t>
+          <t>Z202</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Arm/forearm/wrist splint/cast</t>
+          <t>Hand splint/cast</t>
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
@@ -5979,19 +5979,19 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Only if no F or D code billed; Exact fee $24.10 (MOH Jan 2025)</t>
+          <t>Only if no F or D code billed; Exact fee $14.90 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>Z213</t>
+          <t>Z203</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>Below-knee splint/cast</t>
+          <t>Arm/forearm/wrist splint/cast</t>
         </is>
       </c>
       <c r="C231" s="7" t="n">
@@ -6011,16 +6011,16 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Z211</t>
+          <t>Z213</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Long leg splint/cast</t>
+          <t>Below-knee splint/cast</t>
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
@@ -6029,37 +6029,62 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Only if no F or D code billed; Exact fee $28.80 (MOH Jan 2025)</t>
+          <t>Only if no F or D code billed; Exact fee $24.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
+          <t>Z211</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Long leg splint/cast</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>Splints &amp; Casts</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>Only if no F or D code billed; Exact fee $28.80 (MOH Jan 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
           <t>Z204</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="B234" s="3" t="inlineStr">
         <is>
           <t>Cast removal</t>
         </is>
       </c>
-      <c r="C233" s="7" t="n">
+      <c r="C234" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D233" s="6" t="inlineStr">
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>Exact fee $10.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E233"/>
+  <autoFilter ref="A1:E234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6070,7 +6095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8662,7 +8687,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Foreign body removal – eye</t>
+          <t>Foreign body removal – eye (1 FB)</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -8678,37 +8703,41 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Z432A</t>
+          <t>Z848</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Foreign body removal – vagina (GA)</t>
+          <t>Foreign body removal – eye (2 FBs)</t>
         </is>
       </c>
       <c r="C116" s="7" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
           <t>Foreign Bodies</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr"/>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>Exact fee $45.00 (MOH Jan 2025)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>S547</t>
+          <t>Z432A</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Foreign body removal – urethra</t>
+          <t>Foreign body removal – vagina (GA)</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
@@ -8720,3082 +8749,3103 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t>S547</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Foreign body removal – urethra</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>171</v>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Foreign Bodies</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
           <t>E023C</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>Foreign body removal – vagina with sedation</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Foreign Bodies</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>6 anaesthesia units</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="10" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="B119" s="11" t="n"/>
-      <c r="C119" s="11" t="n"/>
-      <c r="D119" s="11" t="n"/>
-      <c r="E119" s="11" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="B120" s="11" t="n"/>
+      <c r="C120" s="11" t="n"/>
+      <c r="D120" s="11" t="n"/>
+      <c r="E120" s="11" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>F134</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>Pelvis fracture with pelvic binder – with reduction</t>
         </is>
       </c>
-      <c r="C120" s="4" t="n">
+      <c r="C121" s="4" t="n">
         <v>442</v>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>No fee for no-reduction code; Exact fee $442.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>F095</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Femur fracture – with reduction</t>
         </is>
       </c>
-      <c r="C121" s="7" t="n">
+      <c r="C122" s="7" t="n">
         <v>407</v>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>No fee for no-reduction code; Exact fee $407.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>F085</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>Patella fracture (no cast) – no reduction</t>
         </is>
       </c>
-      <c r="C122" s="4" t="n">
+      <c r="C123" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>F078</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>Tibia ± fibula fracture – no reduction</t>
         </is>
       </c>
-      <c r="C123" s="7" t="n">
+      <c r="C124" s="7" t="n">
         <v>116</v>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>Exact fee $115.95 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>F079</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>Tibia ± fibula fracture – with reduction</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n">
+      <c r="C125" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>Exact fee $180.05 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>F082</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Fibula fracture – no reduction</t>
         </is>
       </c>
-      <c r="C125" s="7" t="n">
+      <c r="C126" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>F083</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>Fibula fracture – with reduction</t>
         </is>
       </c>
-      <c r="C126" s="4" t="n">
+      <c r="C127" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>Exact fee $101.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>F074</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Ankle fracture – no reduction</t>
         </is>
       </c>
-      <c r="C127" s="7" t="n">
+      <c r="C128" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>F075</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>Ankle fracture – with reduction</t>
         </is>
       </c>
-      <c r="C128" s="4" t="n">
+      <c r="C129" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>Exact fee $144.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>F104</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>Ankle fracture with plafond burst – with reduction</t>
         </is>
       </c>
-      <c r="C129" s="7" t="n">
+      <c r="C130" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>Exact fee $242.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>F070</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>Calcaneus fracture – no reduction</t>
         </is>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C131" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>Exact fee $97.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>F071</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>Calcaneus fracture – with reduction</t>
         </is>
       </c>
-      <c r="C131" s="7" t="n">
+      <c r="C132" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>Exact fee $161.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>F061</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>Metatarsal fracture (no cast) – no reduction</t>
         </is>
       </c>
-      <c r="C132" s="4" t="n">
+      <c r="C133" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>F062</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>Metatarsal fracture (with cast) – no reduction</t>
         </is>
       </c>
-      <c r="C133" s="7" t="n">
+      <c r="C134" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>F063</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>Metatarsal fracture (with cast) – with reduction</t>
         </is>
       </c>
-      <c r="C134" s="4" t="n">
+      <c r="C135" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Exact fee $98.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>F066</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>Tarsal bone fracture – no reduction</t>
         </is>
       </c>
-      <c r="C135" s="7" t="n">
+      <c r="C136" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>Exact fee $98.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>F067</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>Tarsal bone fracture – with reduction</t>
         </is>
       </c>
-      <c r="C136" s="4" t="n">
+      <c r="C137" s="4" t="n">
         <v>165</v>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>Exact fee $165.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>F056</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>Phalanx toe fracture – no reduction</t>
         </is>
       </c>
-      <c r="C137" s="7" t="n">
+      <c r="C138" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>F058</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>Phalanx toe fracture – with reduction</t>
         </is>
       </c>
-      <c r="C138" s="4" t="n">
+      <c r="C139" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>Exact fee $72.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>E560</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>Phalanx toe – each addl, no reduction</t>
         </is>
       </c>
-      <c r="C139" s="7" t="n">
+      <c r="C140" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D140" s="6" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E140" s="6" t="inlineStr">
         <is>
           <t>Exact fee $12.05 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>E561</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>Phalanx toe – each addl, with reduction</t>
         </is>
       </c>
-      <c r="C140" s="4" t="n">
+      <c r="C141" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Fractures – Lower Extremity</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>Exact fee $14.90 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="10" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="B141" s="11" t="n"/>
-      <c r="C141" s="11" t="n"/>
-      <c r="D141" s="11" t="n"/>
-      <c r="E141" s="11" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="B142" s="11" t="n"/>
+      <c r="C142" s="11" t="n"/>
+      <c r="D142" s="11" t="n"/>
+      <c r="E142" s="11" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>F004</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>Phalanx finger fracture – closed, no reduction</t>
         </is>
       </c>
-      <c r="C142" s="4" t="n">
+      <c r="C143" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>F005</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>Phalanx finger fracture – closed, with reduction</t>
         </is>
       </c>
-      <c r="C143" s="7" t="n">
+      <c r="C144" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E144" s="6" t="inlineStr">
         <is>
           <t>Ortho f/u = 75%; Exact fee $99.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>E558</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t>Phalanx finger – each addl fracture with reduction</t>
         </is>
       </c>
-      <c r="C144" s="4" t="n">
+      <c r="C145" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>Exact fee $22.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>F007</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>Phalanx finger fracture – open, with reduction</t>
         </is>
       </c>
-      <c r="C145" s="7" t="n">
+      <c r="C146" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E146" s="6" t="inlineStr">
         <is>
           <t>Exact fee $298.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>F008</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B147" s="3" t="inlineStr">
         <is>
           <t>Metacarpal fracture – no reduction</t>
         </is>
       </c>
-      <c r="C146" s="4" t="n">
+      <c r="C147" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>F009</t>
         </is>
       </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>Metacarpal fracture – with reduction</t>
         </is>
       </c>
-      <c r="C147" s="7" t="n">
+      <c r="C148" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D148" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E148" s="6" t="inlineStr">
         <is>
           <t>Exact fee $99.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>F012</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>Bennett's fracture – no reduction</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
+      <c r="C149" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E148" s="3" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>F013</t>
         </is>
       </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>Bennett's fracture – with reduction</t>
         </is>
       </c>
-      <c r="C149" s="7" t="n">
+      <c r="C150" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D150" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>Exact fee $119.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>F018</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>Scaphoid fracture – no reduction</t>
         </is>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C151" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E150" s="3" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>F102</t>
         </is>
       </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>Other carpal fracture – no reduction</t>
         </is>
       </c>
-      <c r="C151" s="7" t="n">
+      <c r="C152" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E152" s="6" t="inlineStr">
         <is>
           <t>Exact fee $49.20 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>F016</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>Other carpal fracture – with reduction</t>
         </is>
       </c>
-      <c r="C152" s="4" t="n">
+      <c r="C153" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E152" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>Exact fee $115.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>F027</t>
         </is>
       </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>Colles/Smith fracture – no reduction</t>
         </is>
       </c>
-      <c r="C153" s="7" t="n">
+      <c r="C154" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E154" s="6" t="inlineStr">
         <is>
           <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>F028</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>Colles/Smith fracture – with reduction</t>
         </is>
       </c>
-      <c r="C154" s="4" t="n">
+      <c r="C155" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>Exact fee $109.45 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>F046</t>
         </is>
       </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>Colles/Smith fracture – with reduction + sedation</t>
         </is>
       </c>
-      <c r="C155" s="7" t="n">
+      <c r="C156" s="7" t="n">
         <v>149</v>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D156" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E156" s="6" t="inlineStr">
         <is>
           <t>Exact fee $149.35 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>F031</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>Radius or ulna fracture – no reduction</t>
         </is>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C157" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>Exact fee $81.30 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>F032</t>
         </is>
       </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>Radius or ulna fracture – with reduction</t>
         </is>
       </c>
-      <c r="C157" s="7" t="n">
+      <c r="C158" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D158" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E158" s="6" t="inlineStr">
         <is>
           <t>Exact fee $117.85 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>F034</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>Olecranon fracture – no reduction</t>
         </is>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C159" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E158" s="3" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>Exact fee $126.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>F035</t>
         </is>
       </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>Olecranon fracture – with reduction</t>
         </is>
       </c>
-      <c r="C159" s="7" t="n">
+      <c r="C160" s="7" t="n">
         <v>129</v>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E160" s="6" t="inlineStr">
         <is>
           <t>Exact fee $129.00 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>F029</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>Epicondyle fracture (no cast) – no reduction</t>
         </is>
       </c>
-      <c r="C160" s="4" t="n">
+      <c r="C161" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>Exact fee $67.75 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>F037</t>
         </is>
       </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>Epicondyle fracture (no cast) – with reduction</t>
         </is>
       </c>
-      <c r="C161" s="7" t="n">
+      <c r="C162" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D162" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E162" s="6" t="inlineStr">
         <is>
           <t>Exact fee $126.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>F042</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>Humeral shaft fracture (no cast) – no reduction</t>
         </is>
       </c>
-      <c r="C162" s="4" t="n">
+      <c r="C163" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>Exact fee $67.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>F043</t>
         </is>
       </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="B164" s="6" t="inlineStr">
         <is>
           <t>Humeral shaft fracture (no cast) – with reduction</t>
         </is>
       </c>
-      <c r="C163" s="7" t="n">
+      <c r="C164" s="7" t="n">
         <v>148</v>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D164" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E164" s="6" t="inlineStr">
         <is>
           <t>Exact fee $147.60 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>F053</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>Humeral neck fracture (no cast) – no reduction</t>
         </is>
       </c>
-      <c r="C164" s="4" t="n">
+      <c r="C165" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E164" s="3" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>Exact fee $67.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>F054</t>
         </is>
       </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>Humeral neck fracture (no cast) – with reduction</t>
         </is>
       </c>
-      <c r="C165" s="7" t="n">
+      <c r="C166" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D166" s="6" t="inlineStr">
         <is>
           <t>Fractures – Upper Extremity</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E166" s="6" t="inlineStr">
         <is>
           <t>Exact fee $133.60 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="10" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="B166" s="11" t="n"/>
-      <c r="C166" s="11" t="n"/>
-      <c r="D166" s="11" t="n"/>
-      <c r="E166" s="11" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="B167" s="11" t="n"/>
+      <c r="C167" s="11" t="n"/>
+      <c r="D167" s="11" t="n"/>
+      <c r="E167" s="11" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Z101</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>Abscess I&amp;D – one abscess (LA)</t>
         </is>
       </c>
-      <c r="C167" s="4" t="n">
+      <c r="C168" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E167" s="3" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
         <is>
           <t>Z226</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>Elbow bursa I&amp;D</t>
         </is>
       </c>
-      <c r="C168" s="7" t="n">
+      <c r="C169" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="E169" s="6" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Z102</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>Abscess I&amp;D – one abscess (GA)</t>
         </is>
       </c>
-      <c r="C169" s="4" t="n">
+      <c r="C170" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E169" s="3" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="5" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>Z506</t>
         </is>
       </c>
-      <c r="B170" s="6" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Oral abscess I&amp;D</t>
         </is>
       </c>
-      <c r="C170" s="7" t="n">
+      <c r="C171" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="E171" s="6" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Z173</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>Abscess I&amp;D – two abscesses (LA)</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n">
+      <c r="C172" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>Z714</t>
         </is>
       </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="B173" s="6" t="inlineStr">
         <is>
           <t>Bartholin's cyst I&amp;D (LA)</t>
         </is>
       </c>
-      <c r="C172" s="7" t="n">
+      <c r="C173" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="E173" s="6" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Z174</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>Abscess I&amp;D – 3+ abscesses (LA)</t>
         </is>
       </c>
-      <c r="C173" s="4" t="n">
+      <c r="C174" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>Z715</t>
         </is>
       </c>
-      <c r="B174" s="6" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Bartholin's cyst I&amp;D (GA)</t>
         </is>
       </c>
-      <c r="C174" s="7" t="n">
+      <c r="C175" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="E175" s="6" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Z104</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>Perianal abscess I&amp;D (LA)</t>
         </is>
       </c>
-      <c r="C175" s="4" t="n">
+      <c r="C176" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E175" s="3" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>Was $20.10 → $33.25 (+65%) April 2026</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="5" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>Z140</t>
         </is>
       </c>
-      <c r="B176" s="6" t="inlineStr">
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>Breast abscess I&amp;D (LA)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="n">
+      <c r="C177" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="E177" s="6" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Z105</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>Perianal abscess I&amp;D (GA)</t>
         </is>
       </c>
-      <c r="C177" s="4" t="n">
+      <c r="C178" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>Z740</t>
         </is>
       </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>Breast abscess I&amp;D (GA)</t>
         </is>
       </c>
-      <c r="C178" s="7" t="n">
+      <c r="C179" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="E179" s="6" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Z106</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>Pilonidal abscess I&amp;D (LA)</t>
         </is>
       </c>
-      <c r="C179" s="4" t="n">
+      <c r="C180" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
         <is>
           <t>Z227</t>
         </is>
       </c>
-      <c r="B180" s="6" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>IM abscess/hematoma I&amp;D</t>
         </is>
       </c>
-      <c r="C180" s="7" t="n">
+      <c r="C181" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="E181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Z107</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>Pilonidal abscess I&amp;D (GA)</t>
         </is>
       </c>
-      <c r="C181" s="4" t="n">
+      <c r="C182" s="4" t="n">
         <v>118</v>
       </c>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>Z510</t>
         </is>
       </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Peritonsillar abscess (PTA) drainage</t>
         </is>
       </c>
-      <c r="C182" s="7" t="n">
+      <c r="C183" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="E183" s="6" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Z545</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>Hemorrhoid I&amp;D</t>
         </is>
       </c>
-      <c r="C183" s="4" t="n">
+      <c r="C184" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D183" s="3" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E183" s="3" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
         <is>
           <t>E318</t>
         </is>
       </c>
-      <c r="B184" s="6" t="inlineStr">
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>Pinna hematoma drainage</t>
         </is>
       </c>
-      <c r="C184" s="7" t="n">
+      <c r="C185" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>Incision &amp; Drainage</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="10" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="B185" s="11" t="n"/>
-      <c r="C185" s="11" t="n"/>
-      <c r="D185" s="11" t="n"/>
-      <c r="E185" s="11" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="B186" s="11" t="n"/>
+      <c r="C186" s="11" t="n"/>
+      <c r="D186" s="11" t="n"/>
+      <c r="E186" s="11" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>H960</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>On-call travel – Weekday Day</t>
         </is>
       </c>
-      <c r="C186" s="4" t="n">
+      <c r="C187" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="D186" s="3" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E186" s="3" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Max 2/day</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="5" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
         <is>
           <t>H962</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>On-call travel – Weekday Eve</t>
         </is>
       </c>
-      <c r="C187" s="7" t="n">
+      <c r="C188" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>Max 2</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>H963</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>On-call travel – Wkd/Hol</t>
         </is>
       </c>
-      <c r="C188" s="4" t="n">
+      <c r="C189" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="D188" s="3" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E188" s="3" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Max 4</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="5" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
         <is>
           <t>H964</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>On-call travel – Night</t>
         </is>
       </c>
-      <c r="C189" s="7" t="n">
+      <c r="C190" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>H980</t>
         </is>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>On-call 1st patient – Weekday Day</t>
         </is>
       </c>
-      <c r="C190" s="4" t="n">
+      <c r="C191" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D190" s="3" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E190" s="3" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>Max 5</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="5" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
         <is>
           <t>H984</t>
         </is>
       </c>
-      <c r="B191" s="6" t="inlineStr">
+      <c r="B192" s="6" t="inlineStr">
         <is>
           <t>On-call 1st patient – Weekday Eve</t>
         </is>
       </c>
-      <c r="C191" s="7" t="n">
+      <c r="C192" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D192" s="6" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E192" s="6" t="inlineStr">
         <is>
           <t>Max 5</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>H968</t>
         </is>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>On-call 1st patient – Wkd/Hol</t>
         </is>
       </c>
-      <c r="C192" s="4" t="n">
+      <c r="C193" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="D192" s="3" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E192" s="3" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Max 10</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="5" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
         <is>
           <t>H986</t>
         </is>
       </c>
-      <c r="B193" s="6" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>On-call 1st patient – Night</t>
         </is>
       </c>
-      <c r="C193" s="7" t="n">
+      <c r="C194" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>H981</t>
         </is>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>On-call addl patient – Weekday Day</t>
         </is>
       </c>
-      <c r="C194" s="4" t="n">
+      <c r="C195" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D194" s="3" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E194" s="3" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>Max 5</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="5" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
         <is>
           <t>H985</t>
         </is>
       </c>
-      <c r="B195" s="6" t="inlineStr">
+      <c r="B196" s="6" t="inlineStr">
         <is>
           <t>On-call addl patient – Weekday Eve</t>
         </is>
       </c>
-      <c r="C195" s="7" t="n">
+      <c r="C196" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D196" s="6" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E196" s="6" t="inlineStr">
         <is>
           <t>Max 5</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>H989</t>
         </is>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>On-call addl patient – Wkd/Hol</t>
         </is>
       </c>
-      <c r="C196" s="4" t="n">
+      <c r="C197" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="D196" s="3" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E196" s="3" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>Max 10</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="5" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
         <is>
           <t>H987</t>
         </is>
       </c>
-      <c r="B197" s="6" t="inlineStr">
+      <c r="B198" s="6" t="inlineStr">
         <is>
           <t>On-call addl patient – Night</t>
         </is>
       </c>
-      <c r="C197" s="7" t="n">
+      <c r="C198" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D198" s="6" t="inlineStr">
         <is>
           <t>On-Call</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E198" s="6" t="inlineStr">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="10" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="10" t="inlineStr">
         <is>
           <t>Premiums</t>
         </is>
       </c>
-      <c r="B198" s="11" t="n"/>
-      <c r="C198" s="11" t="n"/>
-      <c r="D198" s="11" t="n"/>
-      <c r="E198" s="11" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="B199" s="11" t="n"/>
+      <c r="C199" s="11" t="n"/>
+      <c r="D199" s="11" t="n"/>
+      <c r="E199" s="11" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>H112</t>
         </is>
       </c>
-      <c r="B199" s="3" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>Night premium (midnight–8am)</t>
         </is>
       </c>
-      <c r="C199" s="4" t="n">
+      <c r="C200" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="D199" s="3" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>Premiums</t>
         </is>
       </c>
-      <c r="E199" s="3" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>Per patient visit</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="5" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
         <is>
           <t>H113</t>
         </is>
       </c>
-      <c r="B200" s="6" t="inlineStr">
+      <c r="B201" s="6" t="inlineStr">
         <is>
           <t>Wkd/Hol + Fri eve premium</t>
         </is>
       </c>
-      <c r="C200" s="7" t="n">
+      <c r="C201" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D201" s="6" t="inlineStr">
         <is>
           <t>Premiums</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E201" s="6" t="inlineStr">
         <is>
           <t>Per patient visit; incl Fri eve 5pm–midnight</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>H114</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>Weekday eve premium (Mon–Thu)</t>
         </is>
       </c>
-      <c r="C201" s="4" t="n">
+      <c r="C202" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>Premiums</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>Per patient visit; NEW April 2026</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="10" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="B202" s="11" t="n"/>
-      <c r="C202" s="11" t="n"/>
-      <c r="D202" s="11" t="n"/>
-      <c r="E202" s="11" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="B203" s="11" t="n"/>
+      <c r="C203" s="11" t="n"/>
+      <c r="D203" s="11" t="n"/>
+      <c r="E203" s="11" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>J149C</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>U/S guided procedure</t>
         </is>
       </c>
-      <c r="C203" s="4" t="n">
+      <c r="C204" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="D203" s="3" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
         <is>
           <t>G269</t>
         </is>
       </c>
-      <c r="B204" s="6" t="inlineStr">
+      <c r="B205" s="6" t="inlineStr">
         <is>
           <t>Central line</t>
         </is>
       </c>
-      <c r="C204" s="7" t="n">
+      <c r="C205" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D204" s="6" t="inlineStr">
+      <c r="D205" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="E205" s="6" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>G224</t>
         </is>
       </c>
-      <c r="B205" s="3" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
         <is>
           <t>Nerve block – ring/small (provides analgesia &gt; 4h)</t>
         </is>
       </c>
-      <c r="C205" s="4" t="n">
+      <c r="C206" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E205" s="3" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
         <is>
           <t>G268</t>
         </is>
       </c>
-      <c r="B206" s="6" t="inlineStr">
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>Arterial line</t>
         </is>
       </c>
-      <c r="C206" s="7" t="n">
+      <c r="C207" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="E207" s="6" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>G060</t>
         </is>
       </c>
-      <c r="B207" s="3" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>Major nerve block (provides analgesia &gt; 4h)</t>
         </is>
       </c>
-      <c r="C207" s="4" t="n">
+      <c r="C208" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="5" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
         <is>
           <t>G061</t>
         </is>
       </c>
-      <c r="B208" s="6" t="inlineStr">
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>Minor nerve block (provides analgesia &gt; 4h)</t>
         </is>
       </c>
-      <c r="C208" s="7" t="n">
+      <c r="C209" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D208" s="6" t="inlineStr">
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E208" s="6" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="E209" s="6" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>G260</t>
         </is>
       </c>
-      <c r="B209" s="3" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>Major plexus block – 3-in-1 (provides analgesia &gt; 4h)</t>
         </is>
       </c>
-      <c r="C209" s="4" t="n">
+      <c r="C210" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="D209" s="3" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E209" s="3" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="5" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
         <is>
           <t>G231</t>
         </is>
       </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="B211" s="6" t="inlineStr">
         <is>
           <t>Dental block</t>
         </is>
       </c>
-      <c r="C210" s="7" t="n">
+      <c r="C211" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D210" s="6" t="inlineStr">
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E210" s="6" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+      <c r="E211" s="6" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>G370</t>
         </is>
       </c>
-      <c r="B211" s="3" t="inlineStr">
+      <c r="B212" s="3" t="inlineStr">
         <is>
           <t>Knee aspiration</t>
         </is>
       </c>
-      <c r="C211" s="4" t="n">
+      <c r="C212" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D211" s="3" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E211" s="3" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
         <is>
           <t>G328</t>
         </is>
       </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>Joint aspiration (not knee)</t>
         </is>
       </c>
-      <c r="C212" s="7" t="n">
+      <c r="C213" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>E446</t>
         </is>
       </c>
-      <c r="B213" s="3" t="inlineStr">
+      <c r="B214" s="3" t="inlineStr">
         <is>
           <t>U/S guided aspiration (addl)</t>
         </is>
       </c>
-      <c r="C213" s="4" t="n">
+      <c r="C214" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>Add-on code</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="5" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
         <is>
           <t>Z080</t>
         </is>
       </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>Wound/ulcer debridement</t>
         </is>
       </c>
-      <c r="C214" s="7" t="n">
+      <c r="C215" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>Z331</t>
         </is>
       </c>
-      <c r="B215" s="3" t="inlineStr">
+      <c r="B216" s="3" t="inlineStr">
         <is>
           <t>Diagnostic thoracentesis</t>
         </is>
       </c>
-      <c r="C215" s="4" t="n">
+      <c r="C216" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="D215" s="3" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E215" s="3" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="5" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
         <is>
           <t>Z332</t>
         </is>
       </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>Therapeutic thoracentesis</t>
         </is>
       </c>
-      <c r="C216" s="7" t="n">
+      <c r="C217" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>Z590</t>
         </is>
       </c>
-      <c r="B217" s="3" t="inlineStr">
+      <c r="B218" s="3" t="inlineStr">
         <is>
           <t>Diagnostic paracentesis</t>
         </is>
       </c>
-      <c r="C217" s="4" t="n">
+      <c r="C218" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="5" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
         <is>
           <t>Z591</t>
         </is>
       </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Therapeutic paracentesis</t>
         </is>
       </c>
-      <c r="C218" s="7" t="n">
+      <c r="C219" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D218" s="6" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+      <c r="E219" s="6" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>G356</t>
         </is>
       </c>
-      <c r="B219" s="3" t="inlineStr">
+      <c r="B220" s="3" t="inlineStr">
         <is>
           <t>NG tube insertion</t>
         </is>
       </c>
-      <c r="C219" s="4" t="n">
+      <c r="C220" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="D219" s="3" t="inlineStr">
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E219" s="3" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="5" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
         <is>
           <t>Z520</t>
         </is>
       </c>
-      <c r="B220" s="6" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
         <is>
           <t>G tube change</t>
         </is>
       </c>
-      <c r="C220" s="7" t="n">
+      <c r="C221" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="D221" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+      <c r="E221" s="6" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>Z538</t>
         </is>
       </c>
-      <c r="B221" s="3" t="inlineStr">
+      <c r="B222" s="3" t="inlineStr">
         <is>
           <t>Hernia reduction</t>
         </is>
       </c>
-      <c r="C221" s="4" t="n">
+      <c r="C222" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D221" s="3" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E221" s="3" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="5" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
         <is>
           <t>Z543</t>
         </is>
       </c>
-      <c r="B222" s="6" t="inlineStr">
+      <c r="B223" s="6" t="inlineStr">
         <is>
           <t>Proctoscopy</t>
         </is>
       </c>
-      <c r="C222" s="7" t="n">
+      <c r="C223" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D222" s="6" t="inlineStr">
+      <c r="D223" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E222" s="6" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="E223" s="6" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>Z110</t>
         </is>
       </c>
-      <c r="B223" s="3" t="inlineStr">
+      <c r="B224" s="3" t="inlineStr">
         <is>
           <t>Subungual hematoma drainage</t>
         </is>
       </c>
-      <c r="C223" s="4" t="n">
+      <c r="C224" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="D223" s="3" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="5" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
         <is>
           <t>Z608</t>
         </is>
       </c>
-      <c r="B224" s="6" t="inlineStr">
+      <c r="B225" s="6" t="inlineStr">
         <is>
           <t>Manual Foley declogging</t>
         </is>
       </c>
-      <c r="C224" s="7" t="n">
+      <c r="C225" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="D224" s="6" t="inlineStr">
+      <c r="D225" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E224" s="6" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+      <c r="E225" s="6" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>Z128</t>
         </is>
       </c>
-      <c r="B225" s="3" t="inlineStr">
+      <c r="B226" s="3" t="inlineStr">
         <is>
           <t>Nail removal</t>
         </is>
       </c>
-      <c r="C225" s="4" t="n">
+      <c r="C226" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="D226" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="5" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>A920</t>
         </is>
       </c>
-      <c r="B226" s="6" t="inlineStr">
+      <c r="B227" s="6" t="inlineStr">
         <is>
           <t>Misoprostol (including assessment)</t>
         </is>
       </c>
-      <c r="C226" s="7" t="n">
+      <c r="C227" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="D226" s="6" t="inlineStr">
+      <c r="D227" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E226" s="6" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+      <c r="E227" s="6" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>Z130</t>
         </is>
       </c>
-      <c r="B227" s="3" t="inlineStr">
+      <c r="B228" s="3" t="inlineStr">
         <is>
           <t>Nail removal + cautery</t>
         </is>
       </c>
-      <c r="C227" s="4" t="n">
+      <c r="C228" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="D227" s="3" t="inlineStr">
+      <c r="D228" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E227" s="3" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="5" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
         <is>
           <t>S756</t>
         </is>
       </c>
-      <c r="B228" s="6" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>Removal of POC from OS</t>
         </is>
       </c>
-      <c r="C228" s="7" t="n">
+      <c r="C229" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="D228" s="6" t="inlineStr">
+      <c r="D229" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E228" s="6" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+      <c r="E229" s="6" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>G313</t>
         </is>
       </c>
-      <c r="B229" s="3" t="inlineStr">
+      <c r="B230" s="3" t="inlineStr">
         <is>
           <t>EKG</t>
         </is>
       </c>
-      <c r="C229" s="4" t="n">
+      <c r="C230" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D229" s="3" t="inlineStr">
+      <c r="D230" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E229" s="3" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>Must be discharged patient</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="5" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
         <is>
           <t>Z804</t>
         </is>
       </c>
-      <c r="B230" s="6" t="inlineStr">
+      <c r="B231" s="6" t="inlineStr">
         <is>
           <t>Lumbar puncture</t>
         </is>
       </c>
-      <c r="C230" s="7" t="n">
+      <c r="C231" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D230" s="6" t="inlineStr">
+      <c r="D231" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+      <c r="E231" s="6" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>Z399</t>
         </is>
       </c>
-      <c r="B231" s="3" t="inlineStr">
+      <c r="B232" s="3" t="inlineStr">
         <is>
           <t>Endoscopy</t>
         </is>
       </c>
-      <c r="C231" s="4" t="n">
+      <c r="C232" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="D231" s="3" t="inlineStr">
+      <c r="D232" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E231" s="3" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="5" t="inlineStr">
+      <c r="E232" s="3" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
         <is>
           <t>L810</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>Description of CSF</t>
         </is>
       </c>
-      <c r="C232" s="7" t="n">
+      <c r="C233" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D232" s="6" t="inlineStr">
+      <c r="D233" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E233" s="6" t="inlineStr">
         <is>
           <t>Exact fee $25.00 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>G435</t>
         </is>
       </c>
-      <c r="B233" s="3" t="inlineStr">
+      <c r="B234" s="3" t="inlineStr">
         <is>
           <t>Tonometry</t>
         </is>
       </c>
-      <c r="C233" s="4" t="n">
+      <c r="C234" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D233" s="3" t="inlineStr">
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E233" s="3" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>Exact fee $5.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="5" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
         <is>
           <t>Z432</t>
         </is>
       </c>
-      <c r="B234" s="6" t="inlineStr">
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>Exam under anaesthesia</t>
         </is>
       </c>
-      <c r="C234" s="7" t="n">
+      <c r="C235" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="D234" s="6" t="inlineStr">
+      <c r="D235" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E234" s="6" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+      <c r="E235" s="6" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>Z756</t>
         </is>
       </c>
-      <c r="B235" s="3" t="inlineStr">
+      <c r="B236" s="3" t="inlineStr">
         <is>
           <t>Rectal disimpaction / fecal disimpaction</t>
         </is>
       </c>
-      <c r="C235" s="4" t="n">
+      <c r="C236" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="D235" s="3" t="inlineStr">
+      <c r="D236" s="3" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E235" s="3" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>Was $36.80 → $46.00 April 2026</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="5" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
         <is>
           <t>H264</t>
         </is>
       </c>
-      <c r="B236" s="6" t="inlineStr">
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>ED pelvic exam with speculum</t>
         </is>
       </c>
-      <c r="C236" s="7" t="n">
+      <c r="C237" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D236" s="6" t="inlineStr">
+      <c r="D237" s="6" t="inlineStr">
         <is>
           <t>Routine Procedures</t>
         </is>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E237" s="6" t="inlineStr">
         <is>
           <t>NEW April 2026</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="10" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="B237" s="11" t="n"/>
-      <c r="C237" s="11" t="n"/>
-      <c r="D237" s="11" t="n"/>
-      <c r="E237" s="11" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+      <c r="B238" s="11" t="n"/>
+      <c r="C238" s="11" t="n"/>
+      <c r="D238" s="11" t="n"/>
+      <c r="E238" s="11" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>Z201</t>
         </is>
       </c>
-      <c r="B238" s="3" t="inlineStr">
+      <c r="B239" s="3" t="inlineStr">
         <is>
           <t>Finger splint/cast</t>
         </is>
       </c>
-      <c r="C238" s="4" t="n">
+      <c r="C239" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D238" s="3" t="inlineStr">
+      <c r="D239" s="3" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E238" s="3" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>Only if no F or D code billed; Exact fee $10.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="5" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
         <is>
           <t>Z202</t>
         </is>
       </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>Hand splint/cast</t>
         </is>
       </c>
-      <c r="C239" s="7" t="n">
+      <c r="C240" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>Only if no F or D code billed; Exact fee $14.90 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>Z203</t>
         </is>
       </c>
-      <c r="B240" s="3" t="inlineStr">
+      <c r="B241" s="3" t="inlineStr">
         <is>
           <t>Arm/forearm/wrist splint/cast</t>
         </is>
       </c>
-      <c r="C240" s="4" t="n">
+      <c r="C241" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D240" s="3" t="inlineStr">
+      <c r="D241" s="3" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E240" s="3" t="inlineStr">
+      <c r="E241" s="3" t="inlineStr">
         <is>
           <t>Only if no F or D code billed; Exact fee $24.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="5" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
         <is>
           <t>Z213</t>
         </is>
       </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>Below-knee splint/cast</t>
         </is>
       </c>
-      <c r="C241" s="7" t="n">
+      <c r="C242" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>Only if no F or D code billed; Exact fee $24.10 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>Z211</t>
         </is>
       </c>
-      <c r="B242" s="3" t="inlineStr">
+      <c r="B243" s="3" t="inlineStr">
         <is>
           <t>Long leg splint/cast</t>
         </is>
       </c>
-      <c r="C242" s="4" t="n">
+      <c r="C243" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="D242" s="3" t="inlineStr">
+      <c r="D243" s="3" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E242" s="3" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>Only if no F or D code billed; Exact fee $28.80 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="5" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
         <is>
           <t>Z204</t>
         </is>
       </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>Cast removal</t>
         </is>
       </c>
-      <c r="C243" s="7" t="n">
+      <c r="C244" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>Splints &amp; Casts</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>Exact fee $10.25 (MOH Jan 2025)</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="B244" s="11" t="n"/>
-      <c r="C244" s="11" t="n"/>
-      <c r="D244" s="11" t="n"/>
-      <c r="E244" s="11" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+      <c r="B245" s="11" t="n"/>
+      <c r="C245" s="11" t="n"/>
+      <c r="D245" s="11" t="n"/>
+      <c r="E245" s="11" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>Z154</t>
         </is>
       </c>
-      <c r="B245" s="3" t="inlineStr">
+      <c r="B246" s="3" t="inlineStr">
         <is>
           <t>Face suture 0–5 cm</t>
         </is>
       </c>
-      <c r="C245" s="4" t="n">
+      <c r="C246" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="D245" s="3" t="inlineStr">
+      <c r="D246" s="3" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E245" s="3" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>Adhesive strips/glue = 50% of fee</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="5" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
         <is>
           <t>Z177</t>
         </is>
       </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="B247" s="6" t="inlineStr">
         <is>
           <t>Face suture 5.1–10 cm</t>
         </is>
       </c>
-      <c r="C246" s="7" t="n">
+      <c r="C247" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="D246" s="6" t="inlineStr">
+      <c r="D247" s="6" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E246" s="6" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+      <c r="E247" s="6" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>Z190</t>
         </is>
       </c>
-      <c r="B247" s="3" t="inlineStr">
+      <c r="B248" s="3" t="inlineStr">
         <is>
           <t>Face suture 10.1–15 cm</t>
         </is>
       </c>
-      <c r="C247" s="4" t="n">
+      <c r="C248" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="D247" s="3" t="inlineStr">
+      <c r="D248" s="3" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E247" s="3" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="5" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
         <is>
           <t>Z192</t>
         </is>
       </c>
-      <c r="B248" s="6" t="inlineStr">
+      <c r="B249" s="6" t="inlineStr">
         <is>
           <t>Face suture &gt; 15 cm</t>
         </is>
       </c>
-      <c r="C248" s="7" t="n">
+      <c r="C249" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="D248" s="6" t="inlineStr">
+      <c r="D249" s="6" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E248" s="6" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+      <c r="E249" s="6" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>Z176</t>
         </is>
       </c>
-      <c r="B249" s="3" t="inlineStr">
+      <c r="B250" s="3" t="inlineStr">
         <is>
           <t>Body suture 0–5 cm</t>
         </is>
       </c>
-      <c r="C249" s="4" t="n">
+      <c r="C250" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D249" s="3" t="inlineStr">
+      <c r="D250" s="3" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E249" s="3" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="5" t="inlineStr">
+      <c r="E250" s="3" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
         <is>
           <t>Z175</t>
         </is>
       </c>
-      <c r="B250" s="6" t="inlineStr">
+      <c r="B251" s="6" t="inlineStr">
         <is>
           <t>Body suture 5.1–10 cm</t>
         </is>
       </c>
-      <c r="C250" s="7" t="n">
+      <c r="C251" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="D250" s="6" t="inlineStr">
+      <c r="D251" s="6" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E250" s="6" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+      <c r="E251" s="6" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>Z179</t>
         </is>
       </c>
-      <c r="B251" s="3" t="inlineStr">
+      <c r="B252" s="3" t="inlineStr">
         <is>
           <t>Body suture 10.1–15 cm</t>
         </is>
       </c>
-      <c r="C251" s="4" t="n">
+      <c r="C252" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="D251" s="3" t="inlineStr">
+      <c r="D252" s="3" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E251" s="3" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="5" t="inlineStr">
+      <c r="E252" s="3" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
         <is>
           <t>Z191</t>
         </is>
       </c>
-      <c r="B252" s="6" t="inlineStr">
+      <c r="B253" s="6" t="inlineStr">
         <is>
           <t>Body suture &gt; 15 cm</t>
         </is>
       </c>
-      <c r="C252" s="7" t="n">
+      <c r="C253" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="D252" s="6" t="inlineStr">
+      <c r="D253" s="6" t="inlineStr">
         <is>
           <t>Sutures</t>
         </is>
       </c>
-      <c r="E252" s="6" t="inlineStr"/>
+      <c r="E253" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <mergeCells count="19">
+    <mergeCell ref="A186:E186"/>
     <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A166:E166"/>
+    <mergeCell ref="A142:E142"/>
     <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A119:E119"/>
-    <mergeCell ref="A237:E237"/>
     <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A198:E198"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A120:E120"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A238:E238"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A141:E141"/>
-    <mergeCell ref="A244:E244"/>
+    <mergeCell ref="A203:E203"/>
     <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A199:E199"/>
     <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A245:E245"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
